--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -39846,32 +39846,32 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>U. ETXARTE ORTEGA</t>
+          <t>V. BAUTISTA URBAEZ</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>0</v>
@@ -39880,7 +39880,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.0246</v>
@@ -39889,7 +39889,7 @@
         <v>0.5</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="29">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>S. MOLINA SOSA</t>
+          <t>U. ETXARTE ORTEGA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -40008,18 +40008,18 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>V. BAUTISTA URBAEZ</t>
+          <t>S. MOLINA SOSA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -40033,7 +40033,7 @@
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
@@ -40042,7 +40042,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0246</v>
@@ -40051,7 +40051,7 @@
         <v>0.5</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -40062,23 +40062,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -40096,7 +40096,7 @@
         <v>-2</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>0.5</v>
@@ -40116,14 +40116,14 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40150,7 +40150,7 @@
         <v>-2</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>0.5</v>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -40294,7 +40294,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>M. PICO MESTRES</t>
+          <t>E. GUILERA SALAT</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -40699,7 +40699,7 @@
         <v>1.1364</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>A. MAGRIÑA GARCIA</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>A. MAGRIÑA GARCIA</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A. FARELL TORRES</t>
+          <t>M. PICO MESTRES</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -40843,7 +40843,7 @@
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>0</v>
@@ -40861,7 +40861,7 @@
         <v>1.1364</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>E. GUILERA SALAT</t>
+          <t>A. FARELL TORRES</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -40926,14 +40926,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -40947,14 +40947,14 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>1</v>
@@ -40980,7 +40980,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -41034,7 +41034,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -41088,14 +41088,14 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -41104,28 +41104,28 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
         <v>0</v>
@@ -41142,7 +41142,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -41158,7 +41158,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -41173,13 +41173,13 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M52" s="9" t="n">
         <v>0</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -40073,7 +40073,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -40116,14 +40116,14 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40150,7 +40150,7 @@
         <v>-2</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>0.5</v>
@@ -40170,23 +40170,23 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -40204,7 +40204,7 @@
         <v>-2</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>0.5</v>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>E. GUILERA SALAT</t>
+          <t>M. PICO MESTRES</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -40699,7 +40699,7 @@
         <v>1.1364</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>E. GUILERA SALAT</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. MAGRIÑA GARCIA</t>
+          <t>A. FARELL TORRES</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>M. PICO MESTRES</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -40843,7 +40843,7 @@
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>0</v>
@@ -40861,7 +40861,7 @@
         <v>1.1364</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A. FARELL TORRES</t>
+          <t>A. MAGRIÑA GARCIA</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -40926,14 +40926,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -40947,14 +40947,14 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>1</v>
@@ -41034,14 +41034,14 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -41055,14 +41055,14 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>1</v>
@@ -41088,7 +41088,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -41104,7 +41104,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -41119,13 +41119,13 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M51" s="9" t="n">
         <v>0</v>
@@ -41142,7 +41142,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -41158,14 +41158,14 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
@@ -41173,13 +41173,13 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M52" s="9" t="n">
         <v>0</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -39900,18 +39900,18 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>I. PEREZ INSAGURBE</t>
+          <t>U. ETXARTE ORTEGA</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -39921,7 +39921,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -39934,7 +39934,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.0246</v>
@@ -39954,7 +39954,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>U. ETXARTE ORTEGA</t>
+          <t>S. MOLINA SOSA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -40008,28 +40008,28 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>S. MOLINA SOSA</t>
+          <t>I. PEREZ INSAGURBE</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
@@ -40042,7 +40042,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0246</v>
@@ -40062,14 +40062,14 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -40096,7 +40096,7 @@
         <v>-2</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>0.5</v>
@@ -40116,7 +40116,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -40127,12 +40127,12 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40170,23 +40170,23 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -40204,7 +40204,7 @@
         <v>-2</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>0.5</v>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>M. PICO MESTRES</t>
+          <t>A. MAGRIÑA GARCIA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -40699,7 +40699,7 @@
         <v>1.1364</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. FARELL TORRES</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>A. FARELL TORRES</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A. MAGRIÑA GARCIA</t>
+          <t>M. PICO MESTRES</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>0</v>
@@ -40915,7 +40915,7 @@
         <v>1.1364</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -40926,14 +40926,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -40947,14 +40947,14 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>1</v>
@@ -40980,7 +40980,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -41034,14 +41034,14 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -41055,14 +41055,14 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>1</v>
@@ -41088,7 +41088,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -41104,14 +41104,14 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
@@ -41119,13 +41119,13 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
         <v>0</v>
@@ -41142,7 +41142,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -41158,7 +41158,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -41173,13 +41173,13 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M52" s="9" t="n">
         <v>0</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -39252,41 +39252,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>A. NDABUKIYE RADJABU</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0.7743</v>
@@ -39295,7 +39295,7 @@
         <v>1.1585</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.1106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -39306,41 +39306,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>A. NDABUKIYE RADJABU</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L18" s="9" t="n">
         <v>0.7743</v>
@@ -39349,7 +39349,7 @@
         <v>1.1585</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>0</v>
+        <v>0.1106</v>
       </c>
     </row>
     <row r="19">
@@ -39900,28 +39900,28 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>U. ETXARTE ORTEGA</t>
+          <t>I. PEREZ INSAGURBE</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -39934,7 +39934,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.0246</v>
@@ -39954,7 +39954,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>S. MOLINA SOSA</t>
+          <t>U. ETXARTE ORTEGA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -40008,18 +40008,18 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>I. PEREZ INSAGURBE</t>
+          <t>S. MOLINA SOSA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
@@ -40042,7 +40042,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0246</v>
@@ -40062,23 +40062,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -40096,7 +40096,7 @@
         <v>-2</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>0.5</v>
@@ -40116,7 +40116,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -40127,12 +40127,12 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40170,23 +40170,23 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -40204,7 +40204,7 @@
         <v>-2</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>0.5</v>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -40294,7 +40294,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A. MAGRIÑA GARCIA</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>A. MAGRIÑA GARCIA</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -40926,14 +40926,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -40947,14 +40947,14 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>1</v>
@@ -40980,7 +40980,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -40996,14 +40996,14 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
       </c>
@@ -41011,13 +41011,13 @@
         <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
         <v>0</v>
@@ -41034,14 +41034,14 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -41055,14 +41055,14 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>1</v>
@@ -41088,7 +41088,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -41104,7 +41104,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -41119,13 +41119,13 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M51" s="9" t="n">
         <v>0</v>
@@ -41142,7 +41142,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -39252,41 +39252,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>A. NDABUKIYE RADJABU</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0.7743</v>
@@ -39295,7 +39295,7 @@
         <v>1.1585</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0</v>
+        <v>0.1106</v>
       </c>
     </row>
     <row r="18">
@@ -39306,41 +39306,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A. NDABUKIYE RADJABU</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
         <v>0.7743</v>
@@ -39349,7 +39349,7 @@
         <v>1.1585</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>0.1106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -39846,14 +39846,14 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>V. BAUTISTA URBAEZ</t>
+          <t>I. PEREZ INSAGURBE</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -39867,11 +39867,11 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>0</v>
@@ -39889,7 +39889,7 @@
         <v>0.5</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -39900,18 +39900,18 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>I. PEREZ INSAGURBE</t>
+          <t>U. ETXARTE ORTEGA</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -39921,7 +39921,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -39934,7 +39934,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.0246</v>
@@ -39954,7 +39954,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>U. ETXARTE ORTEGA</t>
+          <t>S. MOLINA SOSA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -40008,32 +40008,32 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>S. MOLINA SOSA</t>
+          <t>V. BAUTISTA URBAEZ</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
@@ -40042,7 +40042,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0246</v>
@@ -40051,7 +40051,7 @@
         <v>0.5</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="32">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -40073,12 +40073,12 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -40116,7 +40116,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -40127,12 +40127,12 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40170,23 +40170,23 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -40204,7 +40204,7 @@
         <v>-2</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>0.5</v>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -40278,14 +40278,14 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -40312,7 +40312,7 @@
         <v>-2</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>0.5</v>
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>E. GUILERA SALAT</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>E. GUILERA SALAT</t>
+          <t>M. PICO MESTRES</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -40735,7 +40735,7 @@
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>0</v>
@@ -40753,7 +40753,7 @@
         <v>1.1364</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A. FARELL TORRES</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>M. PICO MESTRES</t>
+          <t>A. FARELL TORRES</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>0</v>
@@ -40915,7 +40915,7 @@
         <v>1.1364</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -40926,7 +40926,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -41034,14 +41034,14 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -41055,14 +41055,14 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>1</v>
@@ -41088,14 +41088,14 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -41109,14 +41109,14 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>1</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -39360,41 +39360,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>5</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>1.1585</v>
@@ -39414,41 +39414,41 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>5</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>1.1585</v>
@@ -39846,18 +39846,18 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>I. PEREZ INSAGURBE</t>
+          <t>S. MOLINA SOSA</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -39867,7 +39867,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -39880,7 +39880,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.0246</v>
@@ -39900,28 +39900,28 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>U. ETXARTE ORTEGA</t>
+          <t>I. PEREZ INSAGURBE</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -39934,7 +39934,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.0246</v>
@@ -39954,32 +39954,32 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>S. MOLINA SOSA</t>
+          <t>V. BAUTISTA URBAEZ</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H30" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>0</v>
@@ -39988,7 +39988,7 @@
         <v>2</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>1.0246</v>
@@ -39997,7 +39997,7 @@
         <v>0.5</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="31">
@@ -40008,18 +40008,18 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>V. BAUTISTA URBAEZ</t>
+          <t>U. ETXARTE ORTEGA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -40033,7 +40033,7 @@
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
@@ -40042,7 +40042,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0246</v>
@@ -40051,7 +40051,7 @@
         <v>0.5</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -40073,12 +40073,12 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -40116,7 +40116,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -40127,12 +40127,12 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -40170,7 +40170,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -40181,7 +40181,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -40224,7 +40224,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>E. GUILERA SALAT</t>
+          <t>A. MAGRIÑA GARCIA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>M. PICO MESTRES</t>
+          <t>E. GUILERA SALAT</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -40735,7 +40735,7 @@
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>0</v>
@@ -40753,7 +40753,7 @@
         <v>1.1364</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. MAGRIÑA GARCIA</t>
+          <t>A. TERRÓN MARTINEZ</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A. TERRÓN MARTINEZ</t>
+          <t>A. FARELL TORRES</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A. FARELL TORRES</t>
+          <t>M. PICO MESTRES</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>0</v>
@@ -40915,7 +40915,7 @@
         <v>1.1364</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -41088,14 +41088,14 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -41109,14 +41109,14 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>1</v>
@@ -41142,14 +41142,14 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
@@ -41163,14 +41163,14 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>1</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -49343,41 +49343,41 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>1.0389</v>
@@ -49386,7 +49386,7 @@
         <v>0.6863</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -49397,41 +49397,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>1.0389</v>
@@ -49440,7 +49440,7 @@
         <v>0.6863</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="23">
@@ -50207,18 +50207,18 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>M. MELERO BRAVO</t>
+          <t>A. MAGASSA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -50228,20 +50228,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.9197</v>
@@ -50261,41 +50261,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>A. MAGASSA</t>
+          <t>M. MELERO BRAVO</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0.9197</v>
@@ -50315,7 +50315,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -50331,25 +50331,25 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>0.7837</v>
@@ -50358,7 +50358,7 @@
         <v>0.9197</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="40">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -50380,24 +50380,24 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>-1</v>
@@ -50412,7 +50412,7 @@
         <v>0.9197</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="41">
@@ -50423,18 +50423,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -50444,11 +50444,11 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
@@ -50457,7 +50457,7 @@
         <v>-1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0.7837</v>
@@ -50466,7 +50466,7 @@
         <v>0.9197</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="42">
@@ -50531,23 +50531,23 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -50556,7 +50556,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>1</v>
@@ -50565,7 +50565,7 @@
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.7837</v>
@@ -50574,7 +50574,7 @@
         <v>0.9197</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -51989,7 +51989,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -52000,7 +52000,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -52043,7 +52043,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -52054,7 +52054,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -52691,7 +52691,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>N. BERNAL IBARRIA</t>
+          <t>M. COLL-VINENT OLLE</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -52745,7 +52745,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>M. COLL-VINENT OLLE</t>
+          <t>N. BERNAL IBARRIA</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -52853,14 +52853,14 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
@@ -52874,14 +52874,14 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>1</v>
@@ -52907,7 +52907,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -52923,14 +52923,14 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H87" s="8" t="n">
         <v>0</v>
       </c>
@@ -52938,13 +52938,13 @@
         <v>0</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M87" s="9" t="n">
         <v>0</v>
@@ -52961,7 +52961,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -53015,7 +53015,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -53031,7 +53031,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -53046,13 +53046,13 @@
         <v>0</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M89" s="9" t="n">
         <v>0</v>
@@ -53069,14 +53069,14 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
@@ -53090,14 +53090,14 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="8" t="n">
         <v>1</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -49343,41 +49343,41 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>1.0389</v>
@@ -49386,7 +49386,7 @@
         <v>0.6863</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="22">
@@ -49397,41 +49397,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>1.0389</v>
@@ -49440,7 +49440,7 @@
         <v>0.6863</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -50315,23 +50315,23 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -50340,7 +50340,7 @@
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>1</v>
@@ -50349,7 +50349,7 @@
         <v>-1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>0.7837</v>
@@ -50358,7 +50358,7 @@
         <v>0.9197</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -50369,23 +50369,23 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -50397,13 +50397,13 @@
         <v>2</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>0.7837</v>
@@ -50423,18 +50423,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -50444,11 +50444,11 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
@@ -50457,7 +50457,7 @@
         <v>-1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0.7837</v>
@@ -50466,7 +50466,7 @@
         <v>0.9197</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="42">
@@ -50531,41 +50531,41 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.7837</v>
@@ -50574,7 +50574,7 @@
         <v>0.9197</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="44">
@@ -51611,18 +51611,18 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>I. BEDIA DELGADO</t>
+          <t>J. ANTÓNIO</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -51639,13 +51639,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>8</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="9" t="n">
         <v>1.1628</v>
@@ -51665,18 +51665,18 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>J. ANTÓNIO</t>
+          <t>I. BEDIA DELGADO</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -51693,13 +51693,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>8</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
         <v>1.1628</v>
@@ -51827,23 +51827,23 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -51861,7 +51861,7 @@
         <v>-2</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
         <v>0.5</v>
@@ -51881,7 +51881,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -51892,12 +51892,12 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -51935,14 +51935,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -51969,7 +51969,7 @@
         <v>-2</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>0.5</v>
@@ -52043,7 +52043,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -52054,12 +52054,12 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -52853,14 +52853,14 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
@@ -52874,14 +52874,14 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>1</v>
@@ -52907,14 +52907,14 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
@@ -52923,28 +52923,28 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M87" s="9" t="n">
         <v>0</v>
@@ -52961,7 +52961,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>A. DUDA</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -52977,14 +52977,14 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H88" s="8" t="n">
         <v>0</v>
       </c>
@@ -52992,13 +52992,13 @@
         <v>0</v>
       </c>
       <c r="J88" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M88" s="9" t="n">
         <v>0</v>
@@ -53069,7 +53069,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>A. DUDA</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -49343,41 +49343,41 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>1.0389</v>
@@ -49386,7 +49386,7 @@
         <v>0.6863</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -49397,41 +49397,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>1.0389</v>
@@ -49440,7 +49440,7 @@
         <v>0.6863</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="23">
@@ -50207,41 +50207,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A. MAGASSA</t>
+          <t>M. MELERO BRAVO</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.9197</v>
@@ -50261,18 +50261,18 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>M. MELERO BRAVO</t>
+          <t>A. MAGASSA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -50282,20 +50282,20 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0.9197</v>
@@ -50315,32 +50315,32 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H39" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>1</v>
@@ -50349,7 +50349,7 @@
         <v>-1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>0.7837</v>
@@ -50358,7 +50358,7 @@
         <v>0.9197</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="40">
@@ -50369,23 +50369,23 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>B. ASENSIO SENOSIÁIN</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -50394,16 +50394,16 @@
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>0.7837</v>
@@ -50412,7 +50412,7 @@
         <v>0.9197</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="41">
@@ -50423,18 +50423,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -50444,11 +50444,11 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
@@ -50457,7 +50457,7 @@
         <v>-1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0.7837</v>
@@ -50466,7 +50466,7 @@
         <v>0.9197</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="42">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>B. ASENSIO SENOSIÁIN</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -50488,24 +50488,24 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>-1</v>
@@ -50520,7 +50520,7 @@
         <v>0.9197</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -50531,18 +50531,18 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -50552,11 +50552,11 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -50565,7 +50565,7 @@
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.7837</v>
@@ -50574,7 +50574,7 @@
         <v>0.9197</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="44">
@@ -50585,41 +50585,41 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>R. KALAYDJIEV</t>
+          <t>C. CARRAL MAZA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>0.5591</v>
@@ -50639,41 +50639,41 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>C. CARRAL MAZA</t>
+          <t>R. KALAYDJIEV</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H45" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>-5</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>0.5591</v>
@@ -51071,32 +51071,32 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>P. DITS GARCIA</t>
+          <t>C. ORTAS NET</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>0</v>
@@ -51105,16 +51105,16 @@
         <v>5</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L53" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.5187</v>
+        <v>0.5787</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="54">
@@ -51125,32 +51125,32 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>C. ORTAS NET</t>
+          <t>P. DITS GARCIA</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
@@ -51159,16 +51159,16 @@
         <v>5</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L54" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>0.5787</v>
+        <v>0.5187</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -51827,7 +51827,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -51838,7 +51838,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -51935,23 +51935,23 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -51969,7 +51969,7 @@
         <v>-2</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>0.5</v>
@@ -52043,14 +52043,14 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -52077,7 +52077,7 @@
         <v>-2</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>0.5</v>
@@ -52691,7 +52691,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>M. COLL-VINENT OLLE</t>
+          <t>N. BERNAL IBARRIA</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -52745,7 +52745,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>N. BERNAL IBARRIA</t>
+          <t>M. COLL-VINENT OLLE</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -52853,7 +52853,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>L. MORO SANTANO</t>
+          <t>M. LOPEZ BEVIA</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -52869,14 +52869,14 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H86" s="8" t="n">
         <v>0</v>
       </c>
@@ -52884,13 +52884,13 @@
         <v>0</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>1.1364</v>
+        <v>0</v>
       </c>
       <c r="M86" s="9" t="n">
         <v>0</v>
@@ -52907,14 +52907,14 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>J. FARRANDO PEREZ</t>
+          <t>A. ALGUACIL LOZANO</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
@@ -52928,14 +52928,14 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="8" t="n">
         <v>1</v>
@@ -52961,7 +52961,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>M. LOPEZ BEVIA</t>
+          <t>L. MORO SANTANO</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -52977,7 +52977,7 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -52992,13 +52992,13 @@
         <v>0</v>
       </c>
       <c r="J88" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>0</v>
+        <v>1.1364</v>
       </c>
       <c r="M88" s="9" t="n">
         <v>0</v>
@@ -53015,14 +53015,14 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>A. ALGUACIL LOZANO</t>
+          <t>J. FARRANDO PEREZ</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
@@ -53036,14 +53036,14 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>1</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -56614,32 +56614,32 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>E. CASES REY</t>
+          <t>I. GARRIDO PEREZ</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>0</v>
@@ -56657,7 +56657,7 @@
         <v>0.7962</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0.0512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -56668,32 +56668,32 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>I. GARRIDO PEREZ</t>
+          <t>E. CASES REY</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>0</v>
@@ -56711,7 +56711,7 @@
         <v>0.7962</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="36">
@@ -56722,18 +56722,18 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>R. KALAYDJIEV</t>
+          <t>C. CARRAL MAZA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -56743,20 +56743,20 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>0.7075</v>
@@ -56776,41 +56776,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>C. CARRAL MAZA</t>
+          <t>R. KALAYDJIEV</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>2/3</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7075</v>
@@ -57424,41 +57424,41 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>M. CARRILLO PEREZ</t>
+          <t>J. MUÑOZ PINO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>0.7951</v>
@@ -57478,7 +57478,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PINO</t>
+          <t>B. MOMBLONA MONRABAL</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -57494,19 +57494,19 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>2</v>
@@ -57532,28 +57532,28 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>B. MOMBLONA MONRABAL</t>
+          <t>M. CARRILLO PEREZ</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -57566,7 +57566,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L51" s="9" t="n">
         <v>0.7951</v>
@@ -57694,41 +57694,41 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>B. ASENSIO SENOSIÁIN</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L54" s="9" t="n">
         <v>0.7837</v>
@@ -57737,7 +57737,7 @@
         <v>0.9197</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="55">
@@ -57748,23 +57748,23 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>B. ASENSIO SENOSIÁIN</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -57773,16 +57773,16 @@
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
         <v>0.7837</v>
@@ -57791,7 +57791,7 @@
         <v>0.9197</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="56">
@@ -57802,7 +57802,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -57813,12 +57813,12 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -57827,10 +57827,10 @@
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>-1</v>
@@ -57845,7 +57845,7 @@
         <v>0.9197</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -57856,41 +57856,41 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L57" s="9" t="n">
         <v>0.7837</v>
@@ -57899,7 +57899,7 @@
         <v>0.9197</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="58">
@@ -57910,18 +57910,18 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -57931,11 +57931,11 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>0</v>
@@ -57944,7 +57944,7 @@
         <v>-1</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>0.7837</v>
@@ -57953,7 +57953,7 @@
         <v>0.9197</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="59">
@@ -59530,7 +59530,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -59541,12 +59541,12 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -59584,7 +59584,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -59595,7 +59595,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -59638,23 +59638,23 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -59672,7 +59672,7 @@
         <v>-2</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
         <v>0.5</v>
@@ -59692,23 +59692,23 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -59726,7 +59726,7 @@
         <v>-2</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L91" s="9" t="n">
         <v>0.5</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -56614,32 +56614,32 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>I. GARRIDO PEREZ</t>
+          <t>E. CASES REY</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>0</v>
@@ -56657,7 +56657,7 @@
         <v>0.7962</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="35">
@@ -56668,32 +56668,32 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>E. CASES REY</t>
+          <t>I. GARRIDO PEREZ</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>0</v>
@@ -56711,7 +56711,7 @@
         <v>0.7962</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -56722,41 +56722,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>C. CARRAL MAZA</t>
+          <t>R. KALAYDJIEV</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>2/3</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>0.7075</v>
@@ -56776,18 +56776,18 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>R. KALAYDJIEV</t>
+          <t>C. CARRAL MAZA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -56797,20 +56797,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7075</v>
@@ -57424,7 +57424,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PINO</t>
+          <t>B. MOMBLONA MONRABAL</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -57440,19 +57440,19 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>2</v>
@@ -57478,7 +57478,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>B. MOMBLONA MONRABAL</t>
+          <t>J. MUÑOZ PINO</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -57494,7 +57494,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -57506,7 +57506,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>2</v>
@@ -57532,41 +57532,41 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>M. CARRILLO PEREZ</t>
+          <t>P. CASADEVALL RODRIGUEZ</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
         <v>0.7951</v>
@@ -57586,41 +57586,41 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>P. CASADEVALL RODRIGUEZ</t>
+          <t>M. CARRILLO PEREZ</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L52" s="9" t="n">
         <v>0.7951</v>
@@ -57694,23 +57694,23 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>B. ASENSIO SENOSIÁIN</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -57719,16 +57719,16 @@
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
         <v>0.7837</v>
@@ -57737,7 +57737,7 @@
         <v>0.9197</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="55">
@@ -57748,7 +57748,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>B. ASENSIO SENOSIÁIN</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -57759,21 +57759,21 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H55" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
@@ -57791,7 +57791,7 @@
         <v>0.9197</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="56">
@@ -57802,41 +57802,41 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0.7837</v>
@@ -57845,7 +57845,7 @@
         <v>0.9197</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="57">
@@ -57856,41 +57856,41 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
         <v>0.7837</v>
@@ -57899,7 +57899,7 @@
         <v>0.9197</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -57910,23 +57910,23 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -57938,13 +57938,13 @@
         <v>2</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>0.7837</v>
@@ -59476,7 +59476,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -59487,12 +59487,12 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -59530,7 +59530,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -59541,12 +59541,12 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -59584,23 +59584,23 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -59618,7 +59618,7 @@
         <v>-2</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L89" s="9" t="n">
         <v>0.5</v>
@@ -59638,7 +59638,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -59649,7 +59649,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -59692,14 +59692,14 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -59726,7 +59726,7 @@
         <v>-2</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
         <v>0.5</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -55912,41 +55912,41 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>1.0389</v>
@@ -55955,7 +55955,7 @@
         <v>0.6863</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="22">
@@ -55966,41 +55966,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>1.0389</v>
@@ -56009,7 +56009,7 @@
         <v>0.6863</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -56722,18 +56722,18 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>R. KALAYDJIEV</t>
+          <t>C. CARRAL MAZA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -56743,20 +56743,20 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>0.7075</v>
@@ -56776,41 +56776,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>C. CARRAL MAZA</t>
+          <t>R. KALAYDJIEV</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>6.9</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>2/3</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7075</v>
@@ -57424,28 +57424,28 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>B. MOMBLONA MONRABAL</t>
+          <t>M. CARRILLO PEREZ</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -57458,7 +57458,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>0.7951</v>
@@ -57478,7 +57478,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PINO</t>
+          <t>B. MOMBLONA MONRABAL</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -57494,19 +57494,19 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>2</v>
@@ -57532,7 +57532,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>P. CASADEVALL RODRIGUEZ</t>
+          <t>J. MUÑOZ PINO</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -57560,7 +57560,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>2</v>
@@ -57586,41 +57586,41 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. CARRILLO PEREZ</t>
+          <t>P. CASADEVALL RODRIGUEZ</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
         <v>0.7951</v>
@@ -57748,18 +57748,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -57769,11 +57769,11 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
@@ -57782,7 +57782,7 @@
         <v>-1</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L55" s="9" t="n">
         <v>0.7837</v>
@@ -57791,7 +57791,7 @@
         <v>0.9197</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="56">
@@ -57802,18 +57802,18 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -57823,11 +57823,11 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
@@ -57836,7 +57836,7 @@
         <v>-1</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0.7837</v>
@@ -57845,7 +57845,7 @@
         <v>0.9197</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="57">
@@ -58612,32 +58612,32 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>C. ORTAS NET</t>
+          <t>P. DITS GARCIA</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H71" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="8" t="n">
         <v>0</v>
@@ -58646,16 +58646,16 @@
         <v>5</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>0.5787</v>
+        <v>0.5187</v>
       </c>
       <c r="N71" s="10" t="n">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58666,32 +58666,32 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>P. DITS GARCIA</t>
+          <t>C. ORTAS NET</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="8" t="n">
         <v>0</v>
@@ -58700,16 +58700,16 @@
         <v>5</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L72" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>0.5187</v>
+        <v>0.5787</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>0</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="73">
@@ -59476,7 +59476,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -59487,12 +59487,12 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -59530,7 +59530,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>L. VALLEJO CASARES</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -59541,7 +59541,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -59584,14 +59584,14 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>C. APONTE LÓPEZ</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -59618,7 +59618,7 @@
         <v>-2</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
         <v>0.5</v>
@@ -59638,7 +59638,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>L. VALLEJO CASARES</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -59649,12 +59649,12 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -59692,14 +59692,14 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>C. APONTE LÓPEZ</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -59726,7 +59726,7 @@
         <v>-2</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L91" s="9" t="n">
         <v>0.5</v>

--- a/fulls/full_mestre_lf2b_2026.xlsx
+++ b/fulls/full_mestre_lf2b_2026.xlsx
@@ -55912,41 +55912,41 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>L. FLETA ROBLES</t>
+          <t>A. GONZÁLEZ RAMÍREZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>1.0389</v>
@@ -55955,7 +55955,7 @@
         <v>0.6863</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -55966,41 +55966,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ RAMÍREZ</t>
+          <t>L. FLETA ROBLES</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>1.0389</v>
@@ -56009,7 +56009,7 @@
         <v>0.6863</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="23">
@@ -56614,32 +56614,32 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>E. CASES REY</t>
+          <t>I. GARRIDO PEREZ</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>0</v>
@@ -56657,7 +56657,7 @@
         <v>0.7962</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0.0512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -56668,32 +56668,32 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>I. GARRIDO PEREZ</t>
+          <t>E. CASES REY</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>0</v>
@@ -56711,7 +56711,7 @@
         <v>0.7962</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="36">
@@ -57424,41 +57424,41 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>M. CARRILLO PEREZ</t>
+          <t>J. MUÑOZ PINO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>0.7951</v>
@@ -57478,28 +57478,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>B. MOMBLONA MONRABAL</t>
+          <t>M. CARRILLO PEREZ</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
@@ -57512,7 +57512,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>0.7951</v>
@@ -57532,7 +57532,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PINO</t>
+          <t>P. CASADEVALL RODRIGUEZ</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -57560,7 +57560,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>2</v>
@@ -57586,7 +57586,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>P. CASADEVALL RODRIGUEZ</t>
+          <t>B. MOMBLONA MONRABAL</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -57602,19 +57602,19 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>2</v>
@@ -57694,7 +57694,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>B. ASENSIO SENOSIÁIN</t>
+          <t>A. SMYKOVSKAIA MIGUNOVA</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -57705,24 +57705,24 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-1</v>
@@ -57737,7 +57737,7 @@
         <v>0.9197</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -57748,28 +57748,28 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>M. CARBÓ MEDINA</t>
+          <t>B. ASENSIO SENOSIÁIN</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -57782,7 +57782,7 @@
         <v>-1</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
         <v>0.7837</v>
@@ -57802,23 +57802,23 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>D. GARCIA DOMINGUEZ</t>
+          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -57830,13 +57830,13 @@
         <v>2</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0.7837</v>
@@ -57856,7 +57856,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A. SMYKOVSKAIA MIGUNOVA</t>
+          <t>D. GARCIA DOMINGUEZ</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -57867,24 +57867,24 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H57" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>-1</v>
@@ -57899,7 +57899,7 @@
         <v>0.9197</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="58">
@@ -57910,7 +57910,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>S. FERNANDEZ DE CUEVAS MARTINEZ</t>
+          <t>M. CARBÓ MEDINA</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -57926,25 +57926,25 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>0.7837</v>
@@ -57953,7 +57953,7 @@
         <v>0.9197</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>0.1567</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="59">
@@ -58612,32 +58612,32 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>P. DITS GARCIA</t>
+          <t>C. ORTAS NET</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="8" t="n">
         <v>0</v>
@@ -58646,16 +58646,16 @@
         <v>5</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>0.5187</v>
+        <v>0.5787</v>
       </c>
       <c r="N71" s="10" t="n">
-        <v>0</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="72">
@@ -58666,32 +58666,32 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>C. ORTAS NET</t>
+          <t>P. DITS GARCIA</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H72" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="8" t="n">
         <v>0</v>
@@ -58700,16 +58700,16 @@
         <v>5</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L72" s="9" t="n">
         <v>1.1416</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>0.5787</v>
+        <v>0.5187</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -59476,7 +59476,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>N. SARASUA BLANCO</t>
+          <t>J. ROYALE SACRISTAN</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -59487,12 +59487,12 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -59584,7 +59584,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>J. LEGARRETA DIAZ</t>
+          <t>N. SARASUA BLANCO</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -59595,12 +59595,12 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -59638,7 +59638,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>J. ROYALE SACRISTAN</t>
+          <t>J. LEGARRETA DIAZ</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -59649,7 +59649,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -60718,7 +60718,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>M. COLL-VINENT OLLE</t>
+          <t>N. BERNAL IBARRIA</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -60772,7 +60772,7 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>N. BERNAL IBARRIA</t>
+          <t>M. COLL-VINENT OLLE</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
